--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22335" windowHeight="10185"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17310" windowHeight="7545"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,21 +14,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
-  <x:si>
-    <x:t>Item_BigPotato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>큰당근</x:t>
-  </x:si>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
     <x:t>지역에 나타나는 금화</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
   </x:si>
   <x:si>
     <x:t>화폐</x:t>
@@ -37,28 +58,49 @@
     <x:t>상자</x:t>
   </x:si>
   <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>큰감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>harv_bigCarrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
   </x:si>
   <x:si>
     <x:t>Epic</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
+    <x:t>옥수수다</x:t>
   </x:si>
   <x:si>
     <x:t>Normal</x:t>
@@ -67,79 +109,19 @@
     <x:t>Legend</x:t>
   </x:si>
   <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
     <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>큰 감자다.ᄄᆞᆨ히 의미가 있진 않다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>큰 당근이다.ᄄᆞᆨ히 의미가 있진 않다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -383,7 +365,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -466,7 +447,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -501,7 +481,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -546,7 +525,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -590,7 +568,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -675,7 +652,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -696,7 +672,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -727,7 +702,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1442,80 +1416,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1524,7 +1498,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1534,19 +1508,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1555,7 +1529,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1565,19 +1539,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1586,7 +1560,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1595,19 +1569,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1616,7 +1590,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1626,19 +1600,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1647,7 +1621,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1656,30 +1630,14 @@
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F9" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G9" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="s">
-        <x:v>38</x:v>
-      </x:c>
+      <x:c r="A9" s="6"/>
+      <x:c r="B9" s="6"/>
+      <x:c r="C9" s="6"/>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
+      <x:c r="F9" s="4"/>
+      <x:c r="G9" s="4"/>
+      <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -1687,30 +1645,14 @@
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F10" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G10" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="s">
-        <x:v>32</x:v>
-      </x:c>
+      <x:c r="A10" s="6"/>
+      <x:c r="B10" s="6"/>
+      <x:c r="C10" s="6"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
+      <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17310" windowHeight="7545"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11820"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,114 +14,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
   <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox의 파라미터는 획득할수있는 아이템Id 리스트 
+StatChangeAtk의 파라미터는 음수 양수로 ATK버프 디버프
+StatChangeHp의 파라미터는 음수 양수로 Hp 버프 디버프
+SummonMonster 파라미터는 소환할 수 있는 몬스터의 Id 리스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
   </x:si>
   <x:si>
     <x:t>옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
     <x:t>상자</x:t>
   </x:si>
   <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
   </x:si>
   <x:si>
     <x:t>의문의 모자</x:t>
   </x:si>
   <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
     <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -306,7 +339,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -353,6 +386,15 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -365,6 +407,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -447,6 +490,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -481,6 +525,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -525,6 +570,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -568,6 +614,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -652,6 +699,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -672,6 +720,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -702,6 +751,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1411,85 +1461,102 @@
     <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
     <x:col min="5" max="7" width="12.5703125" style="2"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="16384" width="12.5703125" style="2"/>
+    <x:col min="9" max="9" width="24.85546875" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="56.71484375" style="2" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:10" ht="93.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="12.300000000000001">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J1" s="16" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
         <x:v>0</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1498,10 +1565,14 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
@@ -1511,16 +1582,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1529,7 +1600,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1542,16 +1613,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1560,28 +1631,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I6" s="4"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J6" s="17">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1590,29 +1666,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="18">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1621,10 +1701,14 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I8" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J8" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
